--- a/WebHost/wwwroot/import-excel/施工能耗导入（06）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（06）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35662B3C-B5CB-4ACF-AEA2-0C63C47BDF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D8010E-C839-4D20-9A89-17EE6397D267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>日期</t>
   </si>
@@ -133,6 +133,14 @@
   </si>
   <si>
     <t>停泊发电机累计时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油库存</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -140,12 +148,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="180" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -281,7 +288,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -304,10 +311,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -334,7 +337,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -651,64 +654,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B800CC8-A909-447B-A086-099E135E3E25}">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="7"/>
+    <col min="1" max="1" width="10.625" style="6"/>
     <col min="2" max="4" width="10.625" style="2"/>
-    <col min="5" max="9" width="10.625" style="15"/>
-    <col min="10" max="13" width="12.625" style="15" customWidth="1"/>
+    <col min="5" max="9" width="10.625" style="14"/>
+    <col min="10" max="13" width="12.625" style="14" customWidth="1"/>
     <col min="14" max="16" width="10.625" style="2"/>
     <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
-    <col min="18" max="20" width="10.625" style="2"/>
-    <col min="21" max="21" width="20.625" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="10.625" style="2"/>
+    <col min="18" max="22" width="10.625" style="2"/>
+    <col min="23" max="23" width="20.625" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="10"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="12" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="12" t="s">
+      <c r="F1" s="12"/>
+      <c r="G1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="12" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="12" t="s">
+      <c r="K1" s="12"/>
+      <c r="L1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="12" t="s">
+      <c r="M1" s="12"/>
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="14" t="s">
+      <c r="O1" s="13"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="8" t="s">
+      <c r="R1" s="13"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="8"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="7"/>
     </row>
-    <row r="2" spans="1:21" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:23" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -762,15 +767,22 @@
       <c r="S2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="10" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:I1"/>

--- a/WebHost/wwwroot/import-excel/施工能耗导入（06）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（06）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D8010E-C839-4D20-9A89-17EE6397D267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0BFD74-36BA-4159-A7E8-3B318DCF7036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>柴油库存</t>
   </si>
   <si>
-    <t>滑油日耗</t>
-  </si>
-  <si>
     <t>简要说明</t>
   </si>
   <si>
@@ -88,10 +85,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>淡水日耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>淡水补充</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,10 +117,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>柴油总日耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主发电机累计时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -141,6 +130,18 @@
   </si>
   <si>
     <t>滑油库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油总消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -328,16 +329,16 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -659,8 +660,8 @@
   <cols>
     <col min="1" max="1" width="10.625" style="6"/>
     <col min="2" max="4" width="10.625" style="2"/>
-    <col min="5" max="9" width="10.625" style="14"/>
-    <col min="10" max="13" width="12.625" style="14" customWidth="1"/>
+    <col min="5" max="9" width="10.625" style="11"/>
+    <col min="10" max="13" width="12.625" style="11" customWidth="1"/>
     <col min="14" max="16" width="10.625" style="2"/>
     <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
     <col min="18" max="22" width="10.625" style="2"/>
@@ -671,42 +672,42 @@
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="7"/>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="14"/>
+      <c r="L1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="14"/>
+      <c r="N1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="13"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="13" t="s">
-        <v>14</v>
-      </c>
       <c r="R1" s="13"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="11" t="s">
-        <v>18</v>
+      <c r="S1" s="14"/>
+      <c r="T1" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="U1" s="13"/>
-      <c r="V1" s="12"/>
+      <c r="V1" s="14"/>
       <c r="W1" s="7"/>
     </row>
     <row r="2" spans="1:23" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -723,10 +724,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>4</v>
@@ -735,31 +736,31 @@
         <v>5</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>6</v>
@@ -768,16 +769,16 @@
         <v>7</v>
       </c>
       <c r="T2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="10" t="s">
         <v>8</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/WebHost/wwwroot/import-excel/施工能耗导入（06）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工能耗导入（06）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0BFD74-36BA-4159-A7E8-3B318DCF7036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0149C4E-2842-4C32-BE0F-B69F48F670B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>日期</t>
   </si>
@@ -47,101 +47,106 @@
     <t>船次</t>
   </si>
   <si>
+    <t>检修时间</t>
+  </si>
+  <si>
+    <t>天气影响</t>
+  </si>
+  <si>
+    <t>柴油补充</t>
+  </si>
+  <si>
+    <t>柴油库存</t>
+  </si>
+  <si>
+    <t>简要说明</t>
+  </si>
+  <si>
+    <t>产量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停工时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作业时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锚泊时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主发电机运行时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停泊发电机运行时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主发电机累计时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停泊发电机累计时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油总消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>船方</t>
-  </si>
-  <si>
-    <t>检修时间</t>
-  </si>
-  <si>
-    <t>天气影响</t>
-  </si>
-  <si>
-    <t>柴油补充</t>
-  </si>
-  <si>
-    <t>柴油库存</t>
-  </si>
-  <si>
-    <t>简要说明</t>
-  </si>
-  <si>
-    <t>产量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>施工时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停工时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水（吨）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柴油（吨）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水补充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水库存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油（吨）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>作业时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>锚泊时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待工</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主发电机运行时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停泊发电机运行时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主发电机累计时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>停泊发电机累计时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油补充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油库存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡水消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柴油总消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滑油消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作业量（万元）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -289,7 +294,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -340,6 +345,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -359,9 +368,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -399,7 +408,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -505,7 +514,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -647,7 +656,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -655,62 +664,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B800CC8-A909-447B-A086-099E135E3E25}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="6"/>
-    <col min="2" max="4" width="10.625" style="2"/>
-    <col min="5" max="9" width="10.625" style="11"/>
-    <col min="10" max="13" width="12.625" style="11" customWidth="1"/>
-    <col min="14" max="16" width="10.625" style="2"/>
-    <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
-    <col min="18" max="22" width="10.625" style="2"/>
-    <col min="23" max="23" width="20.625" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="10.625" style="2"/>
+    <col min="2" max="5" width="10.625" style="2"/>
+    <col min="6" max="10" width="10.625" style="11"/>
+    <col min="11" max="14" width="12.625" style="11" customWidth="1"/>
+    <col min="15" max="17" width="10.625" style="2"/>
+    <col min="18" max="18" width="12.625" style="2" customWidth="1"/>
+    <col min="19" max="23" width="10.625" style="2"/>
+    <col min="24" max="24" width="20.625" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="7"/>
       <c r="C1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="12" t="s">
+      <c r="G1" s="14"/>
+      <c r="H1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="12" t="s">
+      <c r="I1" s="13"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="14"/>
+      <c r="M1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="14"/>
+      <c r="O1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="12" t="s">
+      <c r="P1" s="13"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="13"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="13"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="7"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="13"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="7"/>
     </row>
-    <row r="2" spans="1:23" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -720,77 +730,80 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="K2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="T2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" s="10" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
